--- a/data/trans_camb/P74B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 11,64</t>
+          <t>2,46; 11,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 11,01</t>
+          <t>2,38; 11,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -3,83</t>
+          <t>-12,93; -3,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -4,33</t>
+          <t>-13,92; -4,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,9</t>
+          <t>0,68; 9,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 9,56</t>
+          <t>0,93; 9,94</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 103,39</t>
+          <t>17,38; 99,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 96,65</t>
+          <t>16,44; 97,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -4,43</t>
+          <t>-14,16; -4,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -5,01</t>
+          <t>-15,43; -4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 20,5</t>
+          <t>1,48; 21,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 21,96</t>
+          <t>1,98; 22,96</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,61</t>
+          <t>1,67; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,34</t>
+          <t>3,49; 8,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,71; -5,25</t>
+          <t>-26,31; -4,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -0,43</t>
+          <t>-19,67; -0,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,91</t>
+          <t>2,48; 9,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 13,96</t>
+          <t>6,6; 13,41</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,17; 330,86</t>
+          <t>39,42; 372,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,45; 459,45</t>
+          <t>85,0; 482,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,06; -9,71</t>
+          <t>-37,59; -8,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,13; -0,56</t>
+          <t>-28,33; -0,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 85,54</t>
+          <t>15,71; 80,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,39; 120,69</t>
+          <t>41,57; 119,02</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 14,88</t>
+          <t>-2,43; 14,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 14,59</t>
+          <t>0,49; 15,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,19; -1,2</t>
+          <t>-46,74; 0,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -10,53</t>
+          <t>-55,26; -10,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 19,87</t>
+          <t>-0,02; 20,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 16,97</t>
+          <t>-0,27; 16,57</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 487,45</t>
+          <t>-34,67; 412,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 399,07</t>
+          <t>-0,87; 466,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,46; -3,9</t>
+          <t>-52,46; -0,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,64; -16,69</t>
+          <t>-61,53; -18,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 179,51</t>
+          <t>-2,88; 185,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 157,92</t>
+          <t>-3,65; 157,12</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,48</t>
+          <t>2,67; 7,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,26</t>
+          <t>2,69; 7,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -10,59</t>
+          <t>-18,68; -10,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -11,99</t>
+          <t>-20,75; -12,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,33</t>
+          <t>1,73; 7,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,6</t>
+          <t>0,63; 6,48</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,94; 114,05</t>
+          <t>32,56; 111,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,14; 113,3</t>
+          <t>30,73; 112,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -12,99</t>
+          <t>-22,16; -12,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,05; -15,09</t>
+          <t>-24,58; -15,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,72; 25,16</t>
+          <t>5,57; 25,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 22,82</t>
+          <t>1,98; 22,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P74B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 11,24</t>
+          <t>2,47; 11,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 11,12</t>
+          <t>1,73; 11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -3,87</t>
+          <t>-13,09; -4,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -4,12</t>
+          <t>-14,11; -4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,31</t>
+          <t>0,57; 9,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,94</t>
+          <t>0,47; 9,7</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 99,39</t>
+          <t>16,41; 103,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 97,85</t>
+          <t>12,67; 99,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; -4,4</t>
+          <t>-14,51; -5,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -4,78</t>
+          <t>-15,43; -4,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 21,58</t>
+          <t>1,21; 22,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 22,96</t>
+          <t>1,05; 22,82</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,71</t>
+          <t>1,85; 6,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,74</t>
+          <t>3,61; 8,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,31; -4,78</t>
+          <t>-25,46; -5,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,67; -0,02</t>
+          <t>-20,01; -0,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,56</t>
+          <t>2,72; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,41</t>
+          <t>7,01; 13,82</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,42; 372,42</t>
+          <t>45,12; 403,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,0; 482,66</t>
+          <t>82,73; 451,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -8,68</t>
+          <t>-37,08; -10,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,33; -0,02</t>
+          <t>-28,35; -1,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,71; 80,97</t>
+          <t>17,7; 82,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,57; 119,02</t>
+          <t>44,5; 120,55</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 14,42</t>
+          <t>-2,02; 15,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 15,0</t>
+          <t>-0,28; 14,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 0,67</t>
+          <t>-48,13; 0,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-55,26; -10,52</t>
+          <t>-57,96; -10,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 20,04</t>
+          <t>0,65; 20,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 16,57</t>
+          <t>0,49; 16,98</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 412,68</t>
+          <t>-35,13; 439,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 466,52</t>
+          <t>-7,84; 450,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,46; -0,38</t>
+          <t>-51,81; 0,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,53; -18,44</t>
+          <t>-61,81; -17,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 185,29</t>
+          <t>-0,8; 188,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 157,12</t>
+          <t>-1,29; 161,28</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,24</t>
+          <t>2,67; 7,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,42</t>
+          <t>2,77; 7,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -10,18</t>
+          <t>-19,22; -10,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,75; -12,19</t>
+          <t>-21,06; -11,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,49</t>
+          <t>1,6; 7,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,48</t>
+          <t>0,74; 6,68</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,56; 111,92</t>
+          <t>30,14; 116,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,73; 112,14</t>
+          <t>31,22; 111,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -12,55</t>
+          <t>-22,67; -12,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -15,23</t>
+          <t>-24,85; -14,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,57; 25,98</t>
+          <t>4,87; 24,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,98; 22,64</t>
+          <t>2,43; 23,29</t>
         </is>
       </c>
     </row>
